--- a/Data/fullform.xlsx
+++ b/Data/fullform.xlsx
@@ -472,1881 +472,1881 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What is the full form of LIC?</t>
+          <t>What is the full form of VIP?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Life Insurance Corporation</t>
+          <t>Very Important Person</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Life Investment Corporation</t>
+          <t>Very Intelligent Person</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Legal Insurance Corporation</t>
+          <t>Valued Important Person</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Life Income Corporation</t>
+          <t>Verified Important Person</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Life Insurance Corporation</t>
+          <t>Very Important Person</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Insurance company</t>
+          <t>High priority individual</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What is the full form of ITI?</t>
+          <t>What is the full form of Cloud?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Industrial Training Institute</t>
+          <t>Cloud Computing</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>International Training Institute</t>
+          <t>Centralized Hosting Online Utility Data</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Indian Technical Institute</t>
+          <t>Connected Local Online Utility Data</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Industrial Technology Institute</t>
+          <t>Common Hosting Online Utility Data</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Industrial Training Institute</t>
+          <t>Cloud Computing</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Skill training institute</t>
+          <t>Online data storage and processing</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>What is the full form of ML Model?</t>
+          <t>What is the full form of LAN?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Machine Learning Model</t>
+          <t>Local Area Network</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Manual Learning Model</t>
+          <t>Large Area Network</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Modern Learning Model</t>
+          <t>Long Area Network</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mechanical Logic Model</t>
+          <t>Limited Area Network</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Machine Learning Model</t>
+          <t>Local Area Network</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Trained data-based system</t>
+          <t>Network within small area</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What is the full form of RAW?</t>
+          <t>What is the full form of Addr?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Research and Analysis Wing</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Research and Advanced Wing</t>
+          <t>Addition Route</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Regional Analysis Wing</t>
+          <t>Admin Reference</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Research and Action Wing</t>
+          <t>Advanced Direction</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Research and Analysis Wing</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Indian intelligence agency</t>
+          <t>Location details</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>What is the full form of DOB?</t>
+          <t>What is the full form of SaaS?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
+          <t>Software as a Service</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Day of Birth</t>
+          <t>System as a Service</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data of Birth</t>
+          <t>Software and System</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Document of Birth</t>
+          <t>Service as a Software</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
+          <t>Software as a Service</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Person’s birth date</t>
+          <t>Cloud-based software usage</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>What is the full form of ATM?</t>
+          <t>What is the full form of AI?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Automated Teller Machine</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Any Time Money</t>
+          <t>Automated Intelligence</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Auto Transfer Machine</t>
+          <t>Advanced Internet</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Advanced Teller Machine</t>
+          <t>Applied Intelligence</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Automated Teller Machine</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Cash withdrawal machine</t>
+          <t>Machine-based human-like intelligence</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What is the full form of AC?</t>
+          <t>What is the full form of FAQ?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alternating Current</t>
+          <t>Frequently Asked Questions</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Air Conditioner</t>
+          <t>Fast Asked Questions</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Auto Cooling</t>
+          <t>Final Asked Questions</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Advanced Cooling</t>
+          <t>Frequently Answered Questions</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Air Conditioner</t>
+          <t>Frequently Asked Questions</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Cooling appliance</t>
+          <t>Common questions list</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What is the full form of FIR?</t>
+          <t>What is the full form of Smart Home?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>First Information Report</t>
+          <t>Smart Home System</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Final Investigation Report</t>
+          <t>Software Managed Home</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>First Incident Report</t>
+          <t>Systematic Home</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Filed Information Report</t>
+          <t>Service Managed Home</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>First Information Report</t>
+          <t>Smart Home System</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Police complaint report</t>
+          <t>Automated home devices</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What is the full form of Smart TV?</t>
+          <t>What is the full form of CCTV?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Smart Television</t>
+          <t>Closed Circuit Television</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Systematic Television</t>
+          <t>Central Circuit Television</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Service Media Television</t>
+          <t>Control Circuit Television</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Software Managed TV</t>
+          <t>Closed Control Television</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Smart Television</t>
+          <t>Closed Circuit Television</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Internet-enabled TV</t>
+          <t>Surveillance system</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What is the full form of AI Bot?</t>
+          <t>What is the full form of CPU?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Bot</t>
+          <t>Central Processing Unit</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Automated Internet Bot</t>
+          <t>Computer Processing Unit</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Advanced Interaction Bot</t>
+          <t>Central Program Unit</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Artificial Interface Bot</t>
+          <t>Control Processing Unit</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Bot</t>
+          <t>Central Processing Unit</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Automated chat program</t>
+          <t>Main processing unit of a computer</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>What is the full form of OTP?</t>
+          <t>What is the full form of TV?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>One Time Password</t>
+          <t>Television</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Only Time Password</t>
+          <t>Tele Visual</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Online Transfer Password</t>
+          <t>Total Vision</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>One Token Password</t>
+          <t>Technical Video</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>One Time Password</t>
+          <t>Television</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Single-use security code</t>
+          <t>Electronic display device</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>What is the full form of KYC?</t>
+          <t>What is the full form of LED?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Know Your Customer</t>
+          <t>Light Emitting Diode</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Know Your Client</t>
+          <t>Light Energy Diode</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Keep Your Customer</t>
+          <t>Low Emitting Diode</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Know Your Consumer</t>
+          <t>Light Electronic Diode</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Know Your Customer</t>
+          <t>Light Emitting Diode</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Customer verification process</t>
+          <t>Energy-efficient light</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>What is the full form of PAN?</t>
+          <t>What is the full form of OK?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Permanent Account Number</t>
+          <t>Okay</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Personal Account Number</t>
+          <t>All Correct</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Public Account Number</t>
+          <t>Order Known</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Primary Account Number</t>
+          <t>Official Key</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Permanent Account Number</t>
+          <t>Okay</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Tax identification number</t>
+          <t>Agreement or approval</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>What is the full form of OPD?</t>
+          <t>What is the full form of HR?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Out Patient Department</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Outer Patient Department</t>
+          <t>Human Relations</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Official Patient Department</t>
+          <t>Human Rights</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Open Patient Department</t>
+          <t>Human Research</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Out Patient Department</t>
+          <t>Human Resources</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hospital department</t>
+          <t>Employee management department</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>What is the full form of ASAP?</t>
+          <t>What is the full form of RSVP?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>As Soon As Possible</t>
+          <t>Répondez S'il Vous Plaît</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>As Simple As Possible</t>
+          <t>Respond Soon Via Phone</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Anytime Soon As Possible</t>
+          <t>Reply Soon Very Please</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>As Speed As Possible</t>
+          <t>Response Via Same Place</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>As Soon As Possible</t>
+          <t>Répondez S'il Vous Plaît</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Immediately or without delay</t>
+          <t>Please respond</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>What is the full form of IDK?</t>
+          <t>What is the full form of UIDAI?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>I Don’t Know</t>
+          <t>Unique Identification Authority of India</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>I Do Know</t>
+          <t>Universal Identification Authority of India</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I Don’t Knock</t>
+          <t>United Identification Authority of India</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>I Did Know</t>
+          <t>Unique Identity Authority of India</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I Don’t Know</t>
+          <t>Unique Identification Authority of India</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Used when unsure</t>
+          <t>Aadhaar authority</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>What is the full form of ICU?</t>
+          <t>What is the full form of GPS?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Intensive Care Unit</t>
+          <t>Global Positioning System</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Internal Care Unit</t>
+          <t>General Positioning System</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Immediate Care Unit</t>
+          <t>Geographical Positioning System</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Integrated Care Unit</t>
+          <t>Global Path System</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Intensive Care Unit</t>
+          <t>Global Positioning System</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Critical patient ward</t>
+          <t>Location tracking system</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>What is the full form of DOB?</t>
+          <t>What is the full form of UNO?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
+          <t>United Nations Organization</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Day of Birth</t>
+          <t>Universal Nations Organization</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Document of Birth</t>
+          <t>United National Office</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Data of Birth</t>
+          <t>Union Nations Organization</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
+          <t>United Nations Organization</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Birth date</t>
+          <t>International peace body</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>What is the full form of VR?</t>
+          <t>What is the full form of GST?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Virtual Reality</t>
+          <t>Goods and Services Tax</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Visual Reality</t>
+          <t>General Sales Tax</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Verified Reality</t>
+          <t>Global Service Tax</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Virtual Response</t>
+          <t>Goods Service Tariff</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Virtual Reality</t>
+          <t>Goods and Services Tax</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Computer-generated environment</t>
+          <t>Indirect tax system</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>What is the full form of EV?</t>
+          <t>What is the full form of OMG?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Oh My God</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Electronic Vehicle</t>
+          <t>Only My God</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Energy Vehicle</t>
+          <t>On My Ground</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Eco Vehicle</t>
+          <t>Oh My Goodness</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Electric Vehicle</t>
+          <t>Oh My God</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Battery-powered vehicle</t>
+          <t>Expression of surprise</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What is the full form of TV?</t>
+          <t>What is the full form of QR?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Television</t>
+          <t>Quick Response</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Tele Visual</t>
+          <t>Quality Reader</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Total Vision</t>
+          <t>Query Response</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Technical Video</t>
+          <t>Quick Reader</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Television</t>
+          <t>Quick Response</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Electronic display device</t>
+          <t>Fast scannable code</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>What is the full form of GDP?</t>
+          <t>What is the full form of Call?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Gross Domestic Product</t>
+          <t>Calling</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>General Domestic Price</t>
+          <t>Communication Action Link Line</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Global Development Product</t>
+          <t>Connect All Lines</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gross Data Product</t>
+          <t>Contact Action Line</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Gross Domestic Product</t>
+          <t>Calling</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Measure of national income</t>
+          <t>Voice communication</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What is the full form of BPO?</t>
+          <t>What is the full form of GPU?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Business Process Outsourcing</t>
+          <t>Graphics Processing Unit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Business Product Outsourcing</t>
+          <t>General Processing Unit</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Basic Process Outsourcing</t>
+          <t>Graphical Program Unit</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Business Procedure Outsourcing</t>
+          <t>Global Processing Unit</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Business Process Outsourcing</t>
+          <t>Graphics Processing Unit</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Outsourced business service</t>
+          <t>High-speed visual processor</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What is the full form of GDP?</t>
+          <t>What is the full form of Face ID?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product</t>
+          <t>Facial Identification</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Global Domestic Product</t>
+          <t>Face Identity</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>General Domestic Product</t>
+          <t>Feature Identification</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gross Development Product</t>
+          <t>Fast Identity</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product</t>
+          <t>Facial Identification</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Economic indicator</t>
+          <t>Biometric authentication method</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What is the full form of RAM?</t>
+          <t>What is the full form of EMI?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Read Access Memory</t>
+          <t>Easy Monthly Installment</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Random Access Memory</t>
+          <t>Equated Monthly Installment</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Run Access Memory</t>
+          <t>Equal Monthly Installment</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rapid Access Memory</t>
+          <t>Exact Monthly Installment</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Random Access Memory</t>
+          <t>Equated Monthly Installment</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Temporary memory of a computer</t>
+          <t>Monthly loan payment</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What is the full form of IoT?</t>
+          <t>What is the full form of LIC?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Internet of Things</t>
+          <t>Life Insurance Corporation</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Integration of Things</t>
+          <t>Life Investment Corporation</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Internal Online Things</t>
+          <t>Legal Insurance Corporation</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Internet of Tools</t>
+          <t>Life Income Corporation</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Internet of Things</t>
+          <t>Life Insurance Corporation</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Connected smart devices network</t>
+          <t>Insurance company</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What is the full form of BRB?</t>
+          <t>What is the full form of NO.?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Be Right Back</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Bring Right Back</t>
+          <t>Note</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Be Ready Back</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Be Really Busy</t>
+          <t>Name Order</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Be Right Back</t>
+          <t>Number</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Temporary absence</t>
+          <t>Numeric value indicator</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What is the full form of AI?</t>
+          <t>What is the full form of IT?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Advanced Intelligence</t>
+          <t>Internet Technology</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Automatic Intelligence</t>
+          <t>Integrated Technology</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Applied Intelligence</t>
+          <t>Information Tool</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Machine-based intelligence</t>
+          <t>Computer technology field</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>What is the full form of CSS?</t>
+          <t>What is the full form of IoT?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cascading Style Sheets</t>
+          <t>Internet of Things</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Creative Style Sheets</t>
+          <t>Integration of Things</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Colorful Style Sheets</t>
+          <t>Internal Online Things</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Computer Style Sheets</t>
+          <t>Internet of Tools</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cascading Style Sheets</t>
+          <t>Internet of Things</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Web design language</t>
+          <t>Connected smart devices network</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>What is the full form of UPS?</t>
+          <t>What is the full form of OPD?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Uninterruptible Power Supply</t>
+          <t>Out Patient Department</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Universal Power Supply</t>
+          <t>Outer Patient Department</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Unlimited Power Supply</t>
+          <t>Official Patient Department</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Unified Power Supply</t>
+          <t>Open Patient Department</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Uninterruptible Power Supply</t>
+          <t>Out Patient Department</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Backup power device</t>
+          <t>Hospital department</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What is the full form of SaaS?</t>
+          <t>What is the full form of AC?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Software as a Service</t>
+          <t>Alternating Current</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>System as a Service</t>
+          <t>Air Conditioner</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Software and System</t>
+          <t>Auto Cooling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Service as a Software</t>
+          <t>Advanced Cooling</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Software as a Service</t>
+          <t>Air Conditioner</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Cloud-based software usage</t>
+          <t>Cooling appliance</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>What is the full form of URL?</t>
+          <t>What is the full form of PIN?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Uniform Resource Locator</t>
+          <t>Personal Identification Number</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Universal Resource Locator</t>
+          <t>Private Identity Number</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Uniform Resource Link</t>
+          <t>Public Identification Number</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Universal Resource Link</t>
+          <t>Personal Identity Name</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Uniform Resource Locator</t>
+          <t>Personal Identification Number</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Web address</t>
+          <t>Security number for authentication</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What is the full form of HTTPS?</t>
+          <t>What is the full form of GPS Tracker?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hyper Text Transfer Protocol Secure</t>
+          <t>Global Positioning System Tracker</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Hyper Transfer Text Secure</t>
+          <t>General Position System Tracker</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>High Text Transfer Secure</t>
+          <t>Geo Position Sensor Tracker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hyper Tool Transfer Secure</t>
+          <t>Global Path System Tracker</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hyper Text Transfer Protocol Secure</t>
+          <t>Global Positioning System Tracker</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Secure web protocol</t>
+          <t>Real-time location tracking</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>What is the full form of PDF?</t>
+          <t>What is the full form of HTML?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Portable Document Format</t>
+          <t>Hyper Text Markup Language</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Public Document File</t>
+          <t>High Text Markup Language</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Printable Document Format</t>
+          <t>Hyper Transfer Markup Language</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Personal Document File</t>
+          <t>High Transfer Markup Language</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Portable Document Format</t>
+          <t>Hyper Text Markup Language</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>File format for documents</t>
+          <t>Web page structure language</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What is the full form of EMI?</t>
+          <t>What is the full form of AI?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Easy Monthly Installment</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Equated Monthly Installment</t>
+          <t>Advanced Intelligence</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Equal Monthly Installment</t>
+          <t>Automatic Intelligence</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Exact Monthly Installment</t>
+          <t>Applied Intelligence</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Equated Monthly Installment</t>
+          <t>Artificial Intelligence</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Monthly loan payment</t>
+          <t>Machine-based intelligence</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>What is the full form of FYI?</t>
+          <t>What is the full form of UPI?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>For Your Information</t>
+          <t>Unified Payments Interface</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Fix Your Information</t>
+          <t>Universal Payment Interface</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>For You Individually</t>
+          <t>United Payment India</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>From Your Information</t>
+          <t>Unified Pay Integration</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>For Your Information</t>
+          <t>Unified Payments Interface</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Used to share information</t>
+          <t>Instant digital payment system</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>What is the full form of GPS Tracker?</t>
+          <t>What is the full form of Cache?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Global Positioning System Tracker</t>
+          <t>Cache Memory</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>General Position System Tracker</t>
+          <t>Central Access Memory</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Geo Position Sensor Tracker</t>
+          <t>Common Active Hardware Engine</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Global Path System Tracker</t>
+          <t>Cached Access Hardware</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Global Positioning System Tracker</t>
+          <t>Cache Memory</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Real-time location tracking</t>
+          <t>Temporary fast-access storage</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>What is the full form of QR?</t>
+          <t>What is the full form of ATM?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Quick Response</t>
+          <t>Automated Teller Machine</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Quality Reader</t>
+          <t>Any Time Money</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Query Response</t>
+          <t>Auto Transfer Machine</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Quick Reader</t>
+          <t>Advanced Teller Machine</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Quick Response</t>
+          <t>Automated Teller Machine</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Fast scannable code</t>
+          <t>Cash withdrawal machine</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What is the full form of API?</t>
+          <t>What is the full form of AI Assistant?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Application Programming Interface</t>
+          <t>Artificial Intelligence Assistant</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Applied Program Internet</t>
+          <t>Automated Interface Assistant</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Advanced Programming Interface</t>
+          <t>Advanced Interaction Assistant</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Application Process Integration</t>
+          <t>Artificial Information Assistant</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Application Programming Interface</t>
+          <t>Artificial Intelligence Assistant</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Software communication bridge</t>
+          <t>Digital helper</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>What is the full form of Cache?</t>
+          <t>What is the full form of FYI?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cache Memory</t>
+          <t>For Your Information</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Central Access Memory</t>
+          <t>Fix Your Information</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Common Active Hardware Engine</t>
+          <t>For You Individually</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cached Access Hardware</t>
+          <t>From Your Information</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cache Memory</t>
+          <t>For Your Information</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Temporary fast-access storage</t>
+          <t>Used to share information</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What is the full form of CCTV?</t>
+          <t>What is the full form of NGO?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Closed Circuit Television</t>
+          <t>Non Governmental Organization</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Central Circuit Television</t>
+          <t>National Government Organization</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Control Circuit Television</t>
+          <t>New Government Organization</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Closed Control Television</t>
+          <t>Non Global Organization</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Closed Circuit Television</t>
+          <t>Non Governmental Organization</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Surveillance system</t>
+          <t>Independent organization</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What is the full form of UPI?</t>
+          <t>What is the full form of Dept?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Unified Payments Interface</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Universal Payment Interface</t>
+          <t>Deputy</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>United Payment India</t>
+          <t>Deposit</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Unified Pay Integration</t>
+          <t>Development</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Unified Payments Interface</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Instant digital payment system</t>
+          <t>Organizational division</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What is the full form of WHO?</t>
+          <t>What is the full form of Pic?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>World Health Organization</t>
+          <t>Picture</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>World Human Organization</t>
+          <t>Pixel Image Code</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>World Help Organization</t>
+          <t>Photo Information Copy</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>World Hospital Organization</t>
+          <t>Picture Image Code</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>World Health Organization</t>
+          <t>Picture</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Global health body</t>
+          <t>Image or photo</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>What is the full form of PIN?</t>
+          <t>What is the full form of API?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Personal Identification Number</t>
+          <t>Application Programming Interface</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Private Identity Number</t>
+          <t>Applied Program Internet</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Public Identification Number</t>
+          <t>Advanced Programming Interface</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Personal Identity Name</t>
+          <t>Application Process Integration</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Personal Identification Number</t>
+          <t>Application Programming Interface</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Security number for authentication</t>
+          <t>Software communication bridge</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>What is the full form of PCR?</t>
+          <t>What is the full form of AI Chip?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Polymerase Chain Reaction</t>
+          <t>Artificial Intelligence Chip</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Protein Chain Reaction</t>
+          <t>Advanced Integrated Chip</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Polymer Chain Reaction</t>
+          <t>Automated Interface Chip</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Process Chain Reaction</t>
+          <t>Applied Intelligence Chip</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Polymerase Chain Reaction</t>
+          <t>Artificial Intelligence Chip</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>DNA testing method</t>
+          <t>Processor for AI tasks</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>What is the full form of UIDAI?</t>
+          <t>What is the full form of FIR?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Unique Identification Authority of India</t>
+          <t>First Information Report</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Universal Identification Authority of India</t>
+          <t>Final Investigation Report</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>United Identification Authority of India</t>
+          <t>First Incident Report</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Unique Identity Authority of India</t>
+          <t>Filed Information Report</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Unique Identification Authority of India</t>
+          <t>First Information Report</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Aadhaar authority</t>
+          <t>Police complaint report</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>What is the full form of Addr?</t>
+          <t>What is the full form of WAN?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Wide Area Network</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Addition Route</t>
+          <t>World Area Network</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Admin Reference</t>
+          <t>Wireless Area Network</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Advanced Direction</t>
+          <t>Web Area Network</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Address</t>
+          <t>Wide Area Network</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Location details</t>
+          <t>Network over large area</t>
         </is>
       </c>
     </row>
@@ -2356,957 +2356,957 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>What is the full form of IPO?</t>
+          <t>What is the full form of VR?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Initial Public Offering</t>
+          <t>Virtual Reality</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Indian Public Offering</t>
+          <t>Visual Reality</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Internal Public Offering</t>
+          <t>Verified Reality</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Initial Price Offering</t>
+          <t>Virtual Response</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Initial Public Offering</t>
+          <t>Virtual Reality</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Company share launch</t>
+          <t>Computer-generated environment</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>What is the full form of NLP?</t>
+          <t>What is the full form of HTTP?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Natural Language Processing</t>
+          <t>Hyper Text Transfer Protocol</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Neural Language Program</t>
+          <t>High Text Transfer Protocol</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Natural Logic Processing</t>
+          <t>Hyper Transfer Text Protocol</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Network Language Protocol</t>
+          <t>High Transfer Text Protocol</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Natural Language Processing</t>
+          <t>Hyper Text Transfer Protocol</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Understanding human language by machines</t>
+          <t>Web communication protocol</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>What is the full form of ISRO?</t>
+          <t>What is the full form of ATM?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indian Space Research Organisation</t>
+          <t>Any Time Money</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>International Space Research Organisation</t>
+          <t>Automated Teller Machine</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Indian Satellite Research Organisation</t>
+          <t>Auto Transfer Machine</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Integrated Space Research Organisation</t>
+          <t>Advanced Teller Machine</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Indian Space Research Organisation</t>
+          <t>Automated Teller Machine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>India’s space agency</t>
+          <t>Electronic banking machine</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>What is the full form of LED?</t>
+          <t>What is the full form of URL?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Light Emitting Diode</t>
+          <t>Uniform Resource Locator</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Light Energy Diode</t>
+          <t>Universal Resource Locator</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Low Emitting Diode</t>
+          <t>Uniform Resource Link</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Light Electronic Diode</t>
+          <t>Universal Resource Link</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Light Emitting Diode</t>
+          <t>Uniform Resource Locator</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Energy-efficient light</t>
+          <t>Web address</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>What is the full form of CBI?</t>
+          <t>What is the full form of Voice AI?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Central Bureau of Investigation</t>
+          <t>Voice Artificial Intelligence</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Crime Bureau of India</t>
+          <t>Virtual Assistant Interface</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Central Board of Investigation</t>
+          <t>Verified Audio Intelligence</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Crime Branch of India</t>
+          <t>Vocal Automation Interface</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Central Bureau of Investigation</t>
+          <t>Voice Artificial Intelligence</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Indian investigation agency</t>
+          <t>AI that understands speech</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>What is the full form of GPU?</t>
+          <t>What is the full form of BPO?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Graphics Processing Unit</t>
+          <t>Business Process Outsourcing</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>General Processing Unit</t>
+          <t>Business Product Outsourcing</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Graphical Program Unit</t>
+          <t>Basic Process Outsourcing</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Global Processing Unit</t>
+          <t>Business Procedure Outsourcing</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Graphics Processing Unit</t>
+          <t>Business Process Outsourcing</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>High-speed visual processor</t>
+          <t>Outsourced business service</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>What is the full form of AI Chip?</t>
+          <t>What is the full form of DIY?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Chip</t>
+          <t>Do It Yourself</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Advanced Integrated Chip</t>
+          <t>Done In Yesterday</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Automated Interface Chip</t>
+          <t>Design It Yourself</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Applied Intelligence Chip</t>
+          <t>Do In Yourself</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Chip</t>
+          <t>Do It Yourself</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Processor for AI tasks</t>
+          <t>Self-made work</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>What is the full form of AKA?</t>
+          <t>What is the full form of CBI?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Also Known As</t>
+          <t>Central Bureau of Investigation</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Already Known As</t>
+          <t>Crime Bureau of India</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>As Known As</t>
+          <t>Central Board of Investigation</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Always Known As</t>
+          <t>Crime Branch of India</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Also Known As</t>
+          <t>Central Bureau of Investigation</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Another name</t>
+          <t>Indian investigation agency</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>What is the full form of OMG?</t>
+          <t>What is the full form of BTW?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Oh My God</t>
+          <t>By The Way</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Only My God</t>
+          <t>Between The Words</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>On My Ground</t>
+          <t>Before The Work</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Oh My Goodness</t>
+          <t>By The Work</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Oh My God</t>
+          <t>By The Way</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Expression of surprise</t>
+          <t>Used to add extra information</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>What is the full form of Cloud?</t>
+          <t>What is the full form of App?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Cloud Computing</t>
+          <t>Application</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Centralized Hosting Online Utility Data</t>
+          <t>Applied Program</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Connected Local Online Utility Data</t>
+          <t>Approved Program</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Common Hosting Online Utility Data</t>
+          <t>Application Process</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cloud Computing</t>
+          <t>Application</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Online data storage and processing</t>
+          <t>Software program</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>What is the full form of RBI?</t>
+          <t>What is the full form of ETA?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Reserve Bank of India</t>
+          <t>Estimated Time of Arrival</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Royal Bank of India</t>
+          <t>Exact Time of Arrival</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Regional Bank of India</t>
+          <t>Expected Time Action</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Registered Bank of India</t>
+          <t>Estimated Travel Arrival</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Reserve Bank of India</t>
+          <t>Estimated Time of Arrival</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Central bank of India</t>
+          <t>Arrival time estimate</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>What is the full form of GPS?</t>
+          <t>What is the full form of OTP?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Global Positioning System</t>
+          <t>One Time Password</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>General Positioning System</t>
+          <t>Only Time Password</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Geographical Positioning System</t>
+          <t>Online Transfer Password</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Global Path System</t>
+          <t>One Token Password</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Global Positioning System</t>
+          <t>One Time Password</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Location tracking system</t>
+          <t>Single-use security code</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>What is the full form of HR?</t>
+          <t>What is the full form of HTTPS?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Hyper Text Transfer Protocol Secure</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Human Relations</t>
+          <t>Hyper Transfer Text Secure</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Human Rights</t>
+          <t>High Text Transfer Secure</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Human Research</t>
+          <t>Hyper Tool Transfer Secure</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Human Resources</t>
+          <t>Hyper Text Transfer Protocol Secure</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Employee management department</t>
+          <t>Secure web protocol</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>What is the full form of App?</t>
+          <t>What is the full form of Msg?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Message</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Applied Program</t>
+          <t>Messenger</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Approved Program</t>
+          <t>Messaging Service</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Application Process</t>
+          <t>Mail Signal</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Application</t>
+          <t>Message</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Software program</t>
+          <t>Text communication</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>What is the full form of Smart Home?</t>
+          <t>What is the full form of RBI?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Smart Home System</t>
+          <t>Reserve Bank of India</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Software Managed Home</t>
+          <t>Royal Bank of India</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Systematic Home</t>
+          <t>Regional Bank of India</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Service Managed Home</t>
+          <t>Registered Bank of India</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Smart Home System</t>
+          <t>Reserve Bank of India</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Automated home devices</t>
+          <t>Central bank of India</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>What is the full form of GDP?</t>
+          <t>What is the full form of EV?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Gross Domestic Product</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>General Domestic Product</t>
+          <t>Electronic Vehicle</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Global Domestic Product</t>
+          <t>Energy Vehicle</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gross Development Product</t>
+          <t>Eco Vehicle</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Gross Domestic Product</t>
+          <t>Electric Vehicle</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Economic growth indicator</t>
+          <t>Battery-powered vehicle</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>What is the full form of ML?</t>
+          <t>What is the full form of NLP?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Natural Language Processing</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Manual Learning</t>
+          <t>Neural Language Program</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Modern Learning</t>
+          <t>Natural Logic Processing</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mechanical Learning</t>
+          <t>Network Language Protocol</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Natural Language Processing</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Learning from data</t>
+          <t>Understanding human language by machines</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>What is the full form of ETA?</t>
+          <t>What is the full form of GDP?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Estimated Time of Arrival</t>
+          <t>Gross Domestic Product</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Exact Time of Arrival</t>
+          <t>General Domestic Product</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Expected Time Action</t>
+          <t>Global Domestic Product</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Estimated Travel Arrival</t>
+          <t>Gross Development Product</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Estimated Time of Arrival</t>
+          <t>Gross Domestic Product</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Arrival time estimate</t>
+          <t>Economic growth indicator</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>What is the full form of Digital Wallet?</t>
+          <t>What is the full form of ITR?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Digital Wallet</t>
+          <t>Income Tax Return</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Data Integrated Global Interface Tool</t>
+          <t>Individual Tax Return</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Device Integrated Global Wallet</t>
+          <t>Income Transfer Report</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dynamic Internet Gateway Wallet</t>
+          <t>Internal Tax Report</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Digital Wallet</t>
+          <t>Income Tax Return</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Electronic money storage</t>
+          <t>Tax filing document</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What is the full form of VIP?</t>
+          <t>What is the full form of CEO?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Very Important Person</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Very Intelligent Person</t>
+          <t>Central Executive Officer</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Valued Important Person</t>
+          <t>Chief Evaluation Officer</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Verified Important Person</t>
+          <t>Corporate Executive Officer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Very Important Person</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>High priority individual</t>
+          <t>Head of company</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What is the full form of Voice AI?</t>
+          <t>What is the full form of Smart TV?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Voice Artificial Intelligence</t>
+          <t>Smart Television</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Virtual Assistant Interface</t>
+          <t>Systematic Television</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Verified Audio Intelligence</t>
+          <t>Service Media Television</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vocal Automation Interface</t>
+          <t>Software Managed TV</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Voice Artificial Intelligence</t>
+          <t>Smart Television</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>AI that understands speech</t>
+          <t>Internet-enabled TV</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>What is the full form of HTML?</t>
+          <t>What is the full form of DOB?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hyper Text Markup Language</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>High Text Markup Language</t>
+          <t>Day of Birth</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hyper Transfer Markup Language</t>
+          <t>Data of Birth</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>High Transfer Markup Language</t>
+          <t>Document of Birth</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hyper Text Markup Language</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Web page structure language</t>
+          <t>Person’s birth date</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>What is the full form of BTW?</t>
+          <t>What is the full form of IDK?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>By The Way</t>
+          <t>I Don’t Know</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Between The Words</t>
+          <t>I Do Know</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Before The Work</t>
+          <t>I Don’t Knock</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>By The Work</t>
+          <t>I Did Know</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>By The Way</t>
+          <t>I Don’t Know</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Used to add extra information</t>
+          <t>Used when unsure</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What is the full form of RSVP?</t>
+          <t>What is the full form of AKA?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Répondez S'il Vous Plaît</t>
+          <t>Also Known As</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Respond Soon Via Phone</t>
+          <t>Already Known As</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Reply Soon Very Please</t>
+          <t>As Known As</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Response Via Same Place</t>
+          <t>Always Known As</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Répondez S'il Vous Plaît</t>
+          <t>Also Known As</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Please respond</t>
+          <t>Another name</t>
         </is>
       </c>
     </row>
@@ -3352,481 +3352,481 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>What is the full form of Face ID?</t>
+          <t>What is the full form of CSS?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Facial Identification</t>
+          <t>Cascading Style Sheets</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Face Identity</t>
+          <t>Creative Style Sheets</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Feature Identification</t>
+          <t>Colorful Style Sheets</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Fast Identity</t>
+          <t>Computer Style Sheets</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Facial Identification</t>
+          <t>Cascading Style Sheets</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Biometric authentication method</t>
+          <t>Web design language</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>What is the full form of LAN?</t>
+          <t>What is the full form of PCR?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Local Area Network</t>
+          <t>Polymerase Chain Reaction</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Large Area Network</t>
+          <t>Protein Chain Reaction</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Long Area Network</t>
+          <t>Polymer Chain Reaction</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Limited Area Network</t>
+          <t>Process Chain Reaction</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Local Area Network</t>
+          <t>Polymerase Chain Reaction</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Network within small area</t>
+          <t>DNA testing method</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>What is the full form of ATM?</t>
+          <t>What is the full form of PAN?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Any Time Money</t>
+          <t>Permanent Account Number</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Automated Teller Machine</t>
+          <t>Personal Account Number</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Auto Transfer Machine</t>
+          <t>Public Account Number</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Advanced Teller Machine</t>
+          <t>Primary Account Number</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Automated Teller Machine</t>
+          <t>Permanent Account Number</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Electronic banking machine</t>
+          <t>Tax identification number</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>What is the full form of Call?</t>
+          <t>What is the full form of GDP?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Calling</t>
+          <t>Gross Domestic Product</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Communication Action Link Line</t>
+          <t>Global Domestic Product</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Connect All Lines</t>
+          <t>General Domestic Product</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Contact Action Line</t>
+          <t>Gross Development Product</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Calling</t>
+          <t>Gross Domestic Product</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Voice communication</t>
+          <t>Economic indicator</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>What is the full form of AI Assistant?</t>
+          <t>What is the full form of DOB?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Assistant</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Automated Interface Assistant</t>
+          <t>Day of Birth</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Advanced Interaction Assistant</t>
+          <t>Document of Birth</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Artificial Information Assistant</t>
+          <t>Data of Birth</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Assistant</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Digital helper</t>
+          <t>Birth date</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>What is the full form of SMS?</t>
+          <t>What is the full form of GDP?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Short Message Service</t>
+          <t>Gross Domestic Product</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Simple Message Service</t>
+          <t>General Domestic Price</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Single Message Service</t>
+          <t>Global Development Product</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Short Media Service</t>
+          <t>Gross Data Product</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Short Message Service</t>
+          <t>Gross Domestic Product</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Text messaging service</t>
+          <t>Measure of national income</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>What is the full form of IT?</t>
+          <t>What is the full form of PDF?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Portable Document Format</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Internet Technology</t>
+          <t>Public Document File</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Integrated Technology</t>
+          <t>Printable Document Format</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Information Tool</t>
+          <t>Personal Document File</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Portable Document Format</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Computer technology field</t>
+          <t>File format for documents</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>What is the full form of NGO?</t>
+          <t>What is the full form of IPO?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Non Governmental Organization</t>
+          <t>Initial Public Offering</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>National Government Organization</t>
+          <t>Indian Public Offering</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>New Government Organization</t>
+          <t>Internal Public Offering</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Non Global Organization</t>
+          <t>Initial Price Offering</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Non Governmental Organization</t>
+          <t>Initial Public Offering</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Independent organization</t>
+          <t>Company share launch</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>What is the full form of USB?</t>
+          <t>What is the full form of Digital Wallet?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Universal Serial Bus</t>
+          <t>Digital Wallet</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>United Serial Bus</t>
+          <t>Data Integrated Global Interface Tool</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Universal System Bus</t>
+          <t>Device Integrated Global Wallet</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Uniform Serial Bus</t>
+          <t>Dynamic Internet Gateway Wallet</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Universal Serial Bus</t>
+          <t>Digital Wallet</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Standard device connection interface</t>
+          <t>Electronic money storage</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>What is the full form of SIM?</t>
+          <t>What is the full form of URL?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Subscriber Identity Module</t>
+          <t>Uniform Resource Locator</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>System Identity Module</t>
+          <t>Universal Resource Link</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Service Identity Module</t>
+          <t>Unified Resource Locator</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Subscriber Information Module</t>
+          <t>Uniform Resource Link</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Subscriber Identity Module</t>
+          <t>Uniform Resource Locator</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Mobile network chip</t>
+          <t>Website address</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>What is the full form of URL?</t>
+          <t>What is the full form of RAW?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Uniform Resource Locator</t>
+          <t>Research and Analysis Wing</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Universal Resource Link</t>
+          <t>Research and Advanced Wing</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Unified Resource Locator</t>
+          <t>Regional Analysis Wing</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Uniform Resource Link</t>
+          <t>Research and Action Wing</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Uniform Resource Locator</t>
+          <t>Research and Analysis Wing</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Website address</t>
+          <t>Indian intelligence agency</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>What is the full form of OK?</t>
+          <t>What is the full form of UPS?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Okay</t>
+          <t>Uninterruptible Power Supply</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>All Correct</t>
+          <t>Universal Power Supply</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Order Known</t>
+          <t>Unlimited Power Supply</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Official Key</t>
+          <t>Unified Power Supply</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Okay</t>
+          <t>Uninterruptible Power Supply</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Agreement or approval</t>
+          <t>Backup power device</t>
         </is>
       </c>
     </row>
@@ -3872,601 +3872,601 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>What is the full form of GST?</t>
+          <t>What is the full form of USB?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Goods and Services Tax</t>
+          <t>Universal Serial Bus</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>General Sales Tax</t>
+          <t>United Serial Bus</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Global Service Tax</t>
+          <t>Universal System Bus</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Goods Service Tariff</t>
+          <t>Uniform Serial Bus</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goods and Services Tax</t>
+          <t>Universal Serial Bus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Indirect tax system</t>
+          <t>Standard device connection interface</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>What is the full form of Msg?</t>
+          <t>What is the full form of BRB?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Message</t>
+          <t>Be Right Back</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Messenger</t>
+          <t>Bring Right Back</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Messaging Service</t>
+          <t>Be Ready Back</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mail Signal</t>
+          <t>Be Really Busy</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Message</t>
+          <t>Be Right Back</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Text communication</t>
+          <t>Temporary absence</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>What is the full form of FAQ?</t>
+          <t>What is the full form of ML Model?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Frequently Asked Questions</t>
+          <t>Machine Learning Model</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Fast Asked Questions</t>
+          <t>Manual Learning Model</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Final Asked Questions</t>
+          <t>Modern Learning Model</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Frequently Answered Questions</t>
+          <t>Mechanical Logic Model</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Frequently Asked Questions</t>
+          <t>Machine Learning Model</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Common questions list</t>
+          <t>Trained data-based system</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>What is the full form of AI?</t>
+          <t>What is the full form of AR?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Augmented Reality</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Automated Intelligence</t>
+          <t>Advanced Reality</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Advanced Internet</t>
+          <t>Artificial Reality</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Applied Intelligence</t>
+          <t>Alternate Reality</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Artificial Intelligence</t>
+          <t>Augmented Reality</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Machine-based human-like intelligence</t>
+          <t>Digital overlay on real world</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>What is the full form of CEO?</t>
+          <t>What is the full form of SMS?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Short Message Service</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Central Executive Officer</t>
+          <t>Simple Message Service</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Chief Evaluation Officer</t>
+          <t>Single Message Service</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Corporate Executive Officer</t>
+          <t>Short Media Service</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Short Message Service</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Head of company</t>
+          <t>Text messaging service</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>What is the full form of HTTP?</t>
+          <t>What is the full form of ICU?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hyper Text Transfer Protocol</t>
+          <t>Intensive Care Unit</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>High Text Transfer Protocol</t>
+          <t>Internal Care Unit</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hyper Transfer Text Protocol</t>
+          <t>Immediate Care Unit</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>High Transfer Text Protocol</t>
+          <t>Integrated Care Unit</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hyper Text Transfer Protocol</t>
+          <t>Intensive Care Unit</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Web communication protocol</t>
+          <t>Critical patient ward</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>What is the full form of AR?</t>
+          <t>What is the full form of SIM?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Augmented Reality</t>
+          <t>Subscriber Identity Module</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Advanced Reality</t>
+          <t>System Identity Module</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Artificial Reality</t>
+          <t>Service Identity Module</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Alternate Reality</t>
+          <t>Subscriber Information Module</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Augmented Reality</t>
+          <t>Subscriber Identity Module</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Digital overlay on real world</t>
+          <t>Mobile network chip</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>What is the full form of DIY?</t>
+          <t>What is the full form of ML?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Do It Yourself</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Done In Yesterday</t>
+          <t>Manual Learning</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Design It Yourself</t>
+          <t>Modern Learning</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Do In Yourself</t>
+          <t>Mechanical Learning</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Do It Yourself</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Self-made work</t>
+          <t>Learning from data</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>What is the full form of NO.?</t>
+          <t>What is the full form of KYC?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Know Your Customer</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Know Your Client</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Keep Your Customer</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Name Order</t>
+          <t>Know Your Consumer</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Number</t>
+          <t>Know Your Customer</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Numeric value indicator</t>
+          <t>Customer verification process</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>What is the full form of WAN?</t>
+          <t>What is the full form of WHO?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Wide Area Network</t>
+          <t>World Health Organization</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>World Area Network</t>
+          <t>World Human Organization</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Wireless Area Network</t>
+          <t>World Help Organization</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Web Area Network</t>
+          <t>World Hospital Organization</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Wide Area Network</t>
+          <t>World Health Organization</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Network over large area</t>
+          <t>Global health body</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>What is the full form of Dept?</t>
+          <t>What is the full form of RAM?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Read Access Memory</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Deputy</t>
+          <t>Random Access Memory</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Deposit</t>
+          <t>Run Access Memory</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Development</t>
+          <t>Rapid Access Memory</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Department</t>
+          <t>Random Access Memory</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Organizational division</t>
+          <t>Temporary memory of a computer</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>What is the full form of Pic?</t>
+          <t>What is the full form of ITI?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Picture</t>
+          <t>Industrial Training Institute</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Pixel Image Code</t>
+          <t>International Training Institute</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Photo Information Copy</t>
+          <t>Indian Technical Institute</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Picture Image Code</t>
+          <t>Industrial Technology Institute</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picture</t>
+          <t>Industrial Training Institute</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Image or photo</t>
+          <t>Skill training institute</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>What is the full form of CPU?</t>
+          <t>What is the full form of ISRO?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Central Processing Unit</t>
+          <t>Indian Space Research Organisation</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Computer Processing Unit</t>
+          <t>International Space Research Organisation</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Central Program Unit</t>
+          <t>Indian Satellite Research Organisation</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Control Processing Unit</t>
+          <t>Integrated Space Research Organisation</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Central Processing Unit</t>
+          <t>Indian Space Research Organisation</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Main processing unit of a computer</t>
+          <t>India’s space agency</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>What is the full form of ITR?</t>
+          <t>What is the full form of AI Bot?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Income Tax Return</t>
+          <t>Artificial Intelligence Bot</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Individual Tax Return</t>
+          <t>Automated Internet Bot</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Income Transfer Report</t>
+          <t>Advanced Interaction Bot</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Internal Tax Report</t>
+          <t>Artificial Interface Bot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Income Tax Return</t>
+          <t>Artificial Intelligence Bot</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tax filing document</t>
+          <t>Automated chat program</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>What is the full form of UNO?</t>
+          <t>What is the full form of ASAP?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>United Nations Organization</t>
+          <t>As Soon As Possible</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Universal Nations Organization</t>
+          <t>As Simple As Possible</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>United National Office</t>
+          <t>Anytime Soon As Possible</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Union Nations Organization</t>
+          <t>As Speed As Possible</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>United Nations Organization</t>
+          <t>As Soon As Possible</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>International peace body</t>
+          <t>Immediately or without delay</t>
         </is>
       </c>
     </row>
